--- a/results/Int All Data -0.7/Linea_2_permute.xlsx
+++ b/results/Int All Data -0.7/Linea_2_permute.xlsx
@@ -446,1437 +446,1437 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7832976101542264</v>
+        <v>0.7507206889569995</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7569576418512752</v>
+        <v>0.7448574330975837</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7780159323051574</v>
+        <v>0.6987692957530144</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5013240848698955</v>
+        <v>0.6979341064434376</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5055419217906738</v>
+        <v>0.6898346028443563</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5049149625430249</v>
+        <v>0.6846503201122662</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5058554014144983</v>
+        <v>0.5414643128931586</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5055419217906738</v>
+        <v>0.5414643128931586</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5055686269033939</v>
+        <v>0.5415276720821609</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5068553595241254</v>
+        <v>0.5425031941409332</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.507133755960651</v>
+        <v>0.5425031941409332</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5086988850179082</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5225302134314499</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5156200473361213</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5090064301722392</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5086273222975473</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5056634038720668</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5054989841584573</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5052205877219317</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5048018585362107</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5040017524139327</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4996198448659858</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.501397742108901</v>
+        <v>0.4617832382654593</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5010921169299942</v>
+        <v>0.4617832382654593</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5008137204934686</v>
+        <v>0.4617832382654593</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5002569276204174</v>
+        <v>0.4589313765874706</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.490896698340443</v>
+        <v>0.462443011638542</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.4906183019039174</v>
+        <v>0.462443011638542</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5</v>
+        <v>0.4561779572857831</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5</v>
+        <v>0.4561779572857831</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5</v>
+        <v>0.4564212705350099</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5</v>
+        <v>0.4561077909111854</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5</v>
+        <v>0.4592776703367288</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5</v>
+        <v>0.4579207713413995</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5</v>
+        <v>0.4581991677779251</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5</v>
+        <v>0.4573639784683483</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5</v>
+        <v>0.4556370478457876</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5</v>
+        <v>0.4568909663410854</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5</v>
+        <v>0.4593659892062473</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5</v>
+        <v>0.4595391360808764</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5</v>
+        <v>0.459817532517402</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5</v>
+        <v>0.4649712701859234</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5</v>
+        <v>0.4652847498097479</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5</v>
+        <v>0.4641711640636454</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5</v>
+        <v>0.4640659145017489</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5</v>
+        <v>0.4678718294224016</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5</v>
+        <v>0.4477084220594704</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5</v>
+        <v>0.4464194203768737</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5</v>
+        <v>0.4470463796245226</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5</v>
+        <v>0.4465620221879342</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5</v>
+        <v>0.4909350978489294</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5</v>
+        <v>0.4898215121028269</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5</v>
+        <v>0.4898215121028269</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5</v>
+        <v>0.4898215121028269</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5</v>
+        <v>0.4895431156663013</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5</v>
+        <v>0.4898565952901258</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5</v>
+        <v>0.4898565952901258</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5</v>
+        <v>0.4897185316027955</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5</v>
+        <v>0.4890564891678477</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5</v>
+        <v>0.4881511334836732</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5</v>
+        <v>0.4884295299201988</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5</v>
+        <v>0.4881511334836732</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5</v>
+        <v>0.4873702271156384</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5</v>
+        <v>0.4868134342425872</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5</v>
+        <v>0.4879994554251524</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5</v>
+        <v>0.4876859758013279</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5</v>
+        <v>0.4892533739204502</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5</v>
+        <v>0.4832270946931879</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5</v>
+        <v>0.4822866558217146</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5</v>
+        <v>0.4828366415091705</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5</v>
+        <v>0.4826634946345414</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5</v>
+        <v>0.4825559760107798</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5</v>
+        <v>0.4825208928234809</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5</v>
+        <v>0.4835643121949857</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5</v>
+        <v>0.4846710907554929</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5</v>
+        <v>0.4871347683113293</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5</v>
+        <v>0.4862995790017525</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5</v>
+        <v>0.4863346621890512</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5</v>
+        <v>0.4872751010605246</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5</v>
+        <v>0.4866481418128757</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5</v>
+        <v>0.4866130586255769</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5</v>
+        <v>0.4869616214367001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5</v>
+        <v>0.4873101842478234</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5</v>
+        <v>0.4873101842478234</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5</v>
+        <v>0.486996704623999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5</v>
+        <v>0.4856748888159687</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5</v>
+        <v>0.4848396995063918</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5</v>
+        <v>0.4846665526317627</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5</v>
+        <v>0.4846314694444638</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5</v>
+        <v>0.4860562657525256</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5</v>
+        <v>0.4860562657525256</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5</v>
+        <v>0.4863697453763501</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5</v>
+        <v>0.4874482479351537</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5</v>
+        <v>0.4866481418128757</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5</v>
+        <v>0.4934631818530905</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5</v>
+        <v>0.4934631818530905</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5</v>
+        <v>0.4934280986657916</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5</v>
+        <v>0.4932198686038637</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5</v>
+        <v>0.4932900349784614</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5</v>
+        <v>0.493568431414987</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5</v>
+        <v>0.493568431414987</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5</v>
+        <v>0.493568431414987</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5</v>
+        <v>0.4939169942261102</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5</v>
+        <v>0.4942304738499347</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5</v>
+        <v>0.4929765553546369</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5</v>
+        <v>0.4931847854165649</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5</v>
+        <v>0.4934631818530905</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5</v>
+        <v>0.4750743554118871</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5</v>
+        <v>0.4750743554118871</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5</v>
+        <v>0.4750743554118871</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5</v>
+        <v>0.4750743554118871</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5</v>
+        <v>0.4750743554118871</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5</v>
+        <v>0.4753527518484127</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5</v>
+        <v>0.4753527518484127</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.4757934734799031</v>
+        <v>0.4839015296967835</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.4754449106687798</v>
+        <v>0.4844583225698347</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4752366806068519</v>
+        <v>0.4831014235745055</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4752366806068519</v>
+        <v>0.4843553420698033</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4757934734799031</v>
+        <v>0.4840769456332777</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4760718699164287</v>
+        <v>0.4840418624459789</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5172467901501769</v>
+        <v>0.48400677925868</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.517494641523134</v>
+        <v>0.4842851756952056</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5138166667830288</v>
+        <v>0.4842851756952056</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5140950632195544</v>
+        <v>0.5120525584545246</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5140950632195544</v>
+        <v>0.512366038078349</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5141301464068533</v>
+        <v>0.512366038078349</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5132949570972765</v>
+        <v>0.5117390788307001</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5127381642242252</v>
+        <v>0.5091961586528057</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.511589495290824</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.511589495290824</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5100968016700296</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5098534884208028</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5095750919842771</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5095750919842771</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5095750919842771</v>
+        <v>0.4994432071269488</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5049147879998045</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5049147879998045</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5049147879998045</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5049147879998045</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5049147879998045</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5014710502614658</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5017494466979914</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5003925477026622</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -1886,7 +1886,7 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -1896,7 +1896,7 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -1906,7 +1906,7 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -1916,7 +1916,7 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -1926,7 +1926,7 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -1936,7 +1936,7 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -1946,7 +1946,7 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -1956,7 +1956,7 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -1966,7 +1966,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -1976,7 +1976,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B156" t="n">
